--- a/config/yunying/volleyball_tasks.xlsx
+++ b/config/yunying/volleyball_tasks.xlsx
@@ -1273,7 +1273,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>毎日対戦勝利数</t>
+          <t>每日对战胜利数</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>毎日対戦勝利数</t>
+          <t>每日对战胜利数</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>毎日獲得点数</t>
+          <t>每日获得分数</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>毎日対戦参加数</t>
+          <t>每日对战人数</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>プレイヤー対戦勝利数</t>
+          <t>玩家对战胜利数</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>プレイヤー対戦勝利数</t>
+          <t>玩家对战胜利数</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>プレイヤー対戦勝利数</t>
+          <t>玩家对战胜利数</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>冰鬼護に勝利</t>
+          <t>战胜冰鬼护</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>皮卡丘に勝利</t>
+          <t>战胜皮卡丘</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>可達鴨に勝利</t>
+          <t>可达鸭获胜</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>路卡利歐に勝利</t>
+          <t>卡莉战胜欧洲</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>誤ってリングアウト</t>
+          <t>环出错误</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>誤ってリングアウト</t>
+          <t>环出错误</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>誤ってリングアウト</t>
+          <t>环出错误</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>皮卡丘獲勝を使用して勝利</t>
+          <t>使用皮卡丘赢得胜利</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>傑尼龜獲勝を使用して勝利</t>
+          <t>杰尼龟获胜使用胜利</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>瑪力露麗獲勝を使用して勝利</t>
+          <t>使用玛力露丽获胜获胜</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>吉利蛋獲勝を使用して勝利</t>
+          <t>吉利蛋获胜使用吉利蛋获胜</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>参加対戦数</t>
+          <t>参加对战数</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>参加対戦数</t>
+          <t>参加对战数</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>参加対戦数</t>
+          <t>参加对战数</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>スキルで敵を減速</t>
+          <t>用技能减速敌人</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>スキルで敵を減速</t>
+          <t>用技能减速敌人</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>スキルで敵を減速</t>
+          <t>用技能减速敌人</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>スキルで相手に勝利</t>
+          <t>用技能战胜对手</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>スキルで相手に勝利</t>
+          <t>用技能战胜对手</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>スキルで相手に勝利</t>
+          <t>用技能战胜对手</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>全ての累計任務を達成</t>
+          <t>完成所有累计任务</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
